--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136732492</v>
       </c>
       <c r="B3" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136732557</v>
       </c>
       <c r="B4" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136732444</v>
       </c>
       <c r="B5" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1010,49 +1010,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136732444</v>
+        <v>136852045</v>
       </c>
       <c r="B5" t="n">
-        <v>99351</v>
+        <v>58008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kusmorliden, Vb</t>
+          <t>Blåbergsliden , Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756321</v>
+        <v>756343</v>
       </c>
       <c r="R5" t="n">
-        <v>7180693</v>
+        <v>7180695</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,21 +1083,25 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Barksprätt tretå</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,6 +1118,113 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136852045</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136732444</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kusmorliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>756321</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7180693</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136732444</t>
         </is>
@@ -1121,6 +1236,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,46 +786,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136732492</v>
+        <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>756336</v>
+        <v>756570</v>
       </c>
       <c r="R3" t="n">
-        <v>7180706</v>
+        <v>7180916</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,12 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,65 +872,65 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136732492</t>
+          <t>https://artportalen.se/Sighting/136922118</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136732557</v>
+        <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>83343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>756342</v>
+        <v>756415</v>
       </c>
       <c r="R4" t="n">
-        <v>7180694</v>
+        <v>7180935</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,12 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,79 +982,79 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136732557</t>
+          <t>https://artportalen.se/Sighting/136922073</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136852045</v>
+        <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blåbergsliden , Vb</t>
+          <t>Kusmorliden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>756343</v>
+        <v>756309</v>
       </c>
       <c r="R5" t="n">
-        <v>7180695</v>
+        <v>7180709</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,72 +1086,76 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Barksprätt tretå</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136852045</t>
+          <t>https://artportalen.se/Sighting/136921923</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136732444</v>
+        <v>136732492</v>
       </c>
       <c r="B6" t="n">
-        <v>99353</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1164,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>756321</v>
+        <v>756336</v>
       </c>
       <c r="R6" t="n">
-        <v>7180693</v>
+        <v>7180706</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1207,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1226,7 +1224,1025 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136732492</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136732557</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kusmorliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>756342</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7180694</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136732557</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136921875</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kusmorliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>756326</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7180705</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hack i en gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921875</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136921898</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kusmorliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>756326</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7180713</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921898</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136852045</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Blåbergsliden , Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>756343</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7180695</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Barksprätt tretå</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136852045</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136921973</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kusmorliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>756397</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7180957</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921973</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136922055</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kusmorliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>756417</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7180953</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922055</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136922106</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kusmorliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>756468</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7180961</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136922106</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136732444</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kusmorliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>756321</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7180693</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136732444</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136921830</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kusmorliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>756315</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7180701</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921830</t>
         </is>
       </c>
     </row>
@@ -1237,6 +2253,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136732444</v>
       </c>
       <c r="B14" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136732444</v>
       </c>
       <c r="B14" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136732444</v>
       </c>
       <c r="B14" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136732444</v>
       </c>
       <c r="B14" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136732444</v>
       </c>
       <c r="B14" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -2033,7 +2033,7 @@
         <v>136732444</v>
       </c>
       <c r="B14" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136732444</v>
       </c>
       <c r="B14" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136732492</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136732557</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136921875</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136921898</v>
       </c>
       <c r="B9" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136852045</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136921973</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136922055</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136922106</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136732444</v>
       </c>
       <c r="B14" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136732492</v>
       </c>
       <c r="B6" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136732557</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136921875</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>136921898</v>
       </c>
       <c r="B9" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136852045</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>136921973</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136922055</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>136922106</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>136732444</v>
       </c>
       <c r="B14" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -1151,11 +1151,7 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1261,11 +1257,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1371,11 +1363,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1486,11 +1474,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1601,11 +1585,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,11 +1696,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1831,11 +1807,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1946,11 +1918,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136732444</v>
       </c>
       <c r="B14" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136732492</v>
       </c>
       <c r="B6" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136732557</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136921875</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136921898</v>
       </c>
       <c r="B9" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>136852045</v>
       </c>
       <c r="B10" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136921973</v>
       </c>
       <c r="B11" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>136922055</v>
       </c>
       <c r="B12" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>136922106</v>
       </c>
       <c r="B13" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136732444</v>
       </c>
       <c r="B14" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136732583</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136732444</v>
       </c>
       <c r="B14" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136921875</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136921898</v>
       </c>
       <c r="B9" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>136852045</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136921973</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>136922055</v>
       </c>
       <c r="B12" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>136922106</v>
       </c>
       <c r="B13" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136921875</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136921898</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>136852045</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>136921973</v>
       </c>
       <c r="B11" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>136922055</v>
       </c>
       <c r="B12" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>136922106</v>
       </c>
       <c r="B13" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33601-2026 artfynd.xlsx
+++ b/artfynd/A 33601-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136922118</v>
       </c>
       <c r="B3" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136922073</v>
       </c>
       <c r="B4" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136921923</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>136921830</v>
       </c>
       <c r="B15" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
